--- a/ops-data/金鯉躍門_v1.3.1_驗收.xlsx
+++ b/ops-data/金鯉躍門_v1.3.1_驗收.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>遊戲規格書 v1.3、PAR 表 2026-08、Bug 清單 BUG-01</t>
+          <t>遊戲規格書 v1.3、數值規格表 2026-08、Bug 清單 BUG-01</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>結論規則：高嚴重度 Bug 全部關閉、設定與 PAR 表完全一致、數學驗收通過，才可上線。</t>
+          <t>結論規則：高嚴重度 Bug 全部關閉、設定與 數值規格表完全一致、數學驗收通過，才可上線。</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>輪帶停點數與 PAR 表一致</t>
+          <t>輪帶停點數與 數值規格表一致</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>賠率表與 PAR 表一致</t>
+          <t>賠率表與 數值規格表一致</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>PAR 表規格</t>
+          <t>數值規格表</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>資料來源：jinli.db 的 config_par（PAR 表）與 config_build（開發匯出的實際設定）；也可用 queries.sql [Q07] 直接列出不一致項目。</t>
+          <t>資料來源：jinli.db 的 config_par（數值規格表）與 config_build（開發匯出的實際設定）；也可用 queries.sql [Q07] 直接列出不一致項目。</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>數學驗收：100 萬轉模擬 vs PAR 表理論值</t>
+          <t>數學驗收：100 萬轉模擬 vs 數值規格表理論值</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>PAR 表</t>
+          <t>數值規格表</t>
         </is>
       </c>
       <c r="C9" s="19" t="n">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>PAR 表（× 總押注）</t>
+          <t>數值規格表（× 總押注）</t>
         </is>
       </c>
       <c r="C10" s="20" t="n">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>PAR 表</t>
+          <t>數值規格表</t>
         </is>
       </c>
       <c r="C11" s="21" t="n">

--- a/ops-data/金鯉躍門_v1.3.1_驗收.xlsx
+++ b/ops-data/金鯉躍門_v1.3.1_驗收.xlsx
@@ -777,7 +777,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>結論規則：高嚴重度 Bug 全部關閉、設定與 數值規格表完全一致、數學驗收通過，才可上線。</t>
+          <t>結論規則：高嚴重度 Bug 全部關閉、設定與數值規格表完全一致、數學驗收通過，才可上線。</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>輪帶停點數與 數值規格表一致</t>
+          <t>輪帶停點數與數值規格表一致</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>賠率表與 數值規格表一致</t>
+          <t>賠率表與數值規格表一致</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
